--- a/files/17-900-n-orange-grove-ave.xlsx
+++ b/files/17-900-n-orange-grove-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD51792A-4A11-4C20-BDD8-01D5C09A9A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5F925DF-1DA0-47A1-B2B7-44444FE49FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7C53C9FB-C9B0-4A68-89A7-73A97D78A016}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0FB7AB8E-E91A-4826-8E9C-AE1E3B28B9AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
   <si>
     <t>LAAA UNDERWRITING BENCHMARKS (edit here; every deal tab reads these)</t>
   </si>
@@ -192,10 +192,10 @@
     <t>LoopNet listing</t>
   </si>
   <si>
-    <t>Data pulled 9/17/2026 from LoopNet public listing</t>
-  </si>
-  <si>
-    <t>NOTE: First sale in 38 years</t>
+    <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Marcus &amp; Millichap, Aug 2026)</t>
+  </si>
+  <si>
+    <t>NOTE: First sale in 38 years | OM: Unit 21 (1 Bd / 1 Ba) is vacant; OM asking rent $2,300 used as its current rent, per OM convention (OM totals include it in scheduled rent).; Cross-check: sum of 20 unit rents = $33,311/mo ($399,732/yr) vs OM stated $33,310/mo and $399,722/yr GPR; difference is rounding, well within 1%.; Rent roll f | OM: Unit 21 (1 Bd / 1 Ba) is vacant; OM asking rent $2,300 used as its current rent, per OM convention (OM totals include it in scheduled rent).; Cross-check: sum of 20 unit rents = $33,311/mo ($399,732/yr) vs OM stated $33,310/mo and $399,722/yr GPR; difference is rounding, well within 1%.; Rent roll f</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -297,19 +297,19 @@
     <t>Rent source</t>
   </si>
   <si>
-    <t>Studio  (~520 SF)</t>
-  </si>
-  <si>
-    <t>Allocated from published GRM (price / GRM) using LAAA bed weights</t>
-  </si>
-  <si>
-    <t>1 Bd / 1 Ba  (~720 SF)</t>
-  </si>
-  <si>
-    <t>2 Bd / 1 Ba  (~900 SF)</t>
-  </si>
-  <si>
-    <t>2 Bd / 2 Ba  (~900 SF)</t>
+    <t>Studio / 1 Ba  (~520 SF)  [units 5, 6, 16, 17; range $833 to $1,575]</t>
+  </si>
+  <si>
+    <t>OM rent roll, current in-place rents (OM Aug 2026)</t>
+  </si>
+  <si>
+    <t>1 Bd / 1 Ba  (~720 SF)  [units 1-3, 8-12, 14, 15, 19-21; unit 8 is 900 SF, rest 720 S]</t>
+  </si>
+  <si>
+    <t>2 Bd / 1 Ba  (~900 SF)  [units 7, 18]</t>
+  </si>
+  <si>
+    <t>2 Bd / 2 Ba  (~900 SF)  [unit 4]</t>
   </si>
   <si>
     <t>Total / weighted avg</t>
@@ -330,7 +330,7 @@
     <t>Scheduled gross rent</t>
   </si>
   <si>
-    <t>OM column: price / published GRM</t>
+    <t>OM column: OM stated current scheduled rent (OM Aug 2026); LAAA column: OM rent roll by unit type</t>
   </si>
   <si>
     <t>Other income (laundry, parking, RUBS)</t>
@@ -342,7 +342,7 @@
     <t>Vacancy &amp; credit loss</t>
   </si>
   <si>
-    <t>OM 3.0% (OM figure if extracted, else 3% assumed); LAAA per Assumptions</t>
+    <t>OM 2.0%; LAAA per Assumptions</t>
   </si>
   <si>
     <t>Effective gross income</t>
@@ -387,7 +387,7 @@
     <t>Utilities (water/sewer/trash/common electric &amp; gas)</t>
   </si>
   <si>
-    <t>per unit, by city</t>
+    <t>per unit, by city; OM utilities + water/sewer + gas/electric + trash combined</t>
   </si>
   <si>
     <t>Contract services (landscape, pest, cleaning)</t>
@@ -396,10 +396,10 @@
     <t>per unit</t>
   </si>
   <si>
-    <t>Admin / legal / licenses / rent registration</t>
-  </si>
-  <si>
-    <t>per unit; OM "other" items land here</t>
+    <t>Admin / legal / licenses / rent registration / other OM items</t>
+  </si>
+  <si>
+    <t>OM other items: On Site Manager 13,200; Pool 4,320; Rent Registration 2,880</t>
   </si>
   <si>
     <t>Replacement reserves</t>
@@ -408,7 +408,7 @@
     <t>Total operating expenses</t>
   </si>
   <si>
-    <t>OM line items not published. OM total IMPLIED = OM EGI - (price x published cap)</t>
+    <t>OM line items from OM (OM Aug 2026); basis: OM 'Current' column on the Income and Expense page (p29) and Financial Overview (p30); taxes, R&amp;M and off-site management are marked '*Estimated' by the OM (taxes = 1.1751% of list price; off-site management = 4.0% of GPR); other lines are presented as actuals. Utilities is one combined line (power, gas and water; water master metered, gas and electric separately metered). Pro forma column differs only in management ($22,502).; OM total 174,070</t>
   </si>
   <si>
     <t>Expenses per unit</t>
@@ -424,6 +424,9 @@
   </si>
   <si>
     <t>Net operating income</t>
+  </si>
+  <si>
+    <t>OM states NOI 220,658 / cap 5.32</t>
   </si>
   <si>
     <t>Cap rate on asking price</t>
@@ -472,12 +475,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,6 +529,7 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -533,8 +538,21 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -562,7 +580,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -598,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -622,12 +641,15 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,7 +682,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{594DD2AA-874B-4010-844D-E0AB66B397B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69CC0E20-B427-41A2-9D1C-C18C64CC5E2F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -971,7 +993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCAD99A-7D71-4455-8A3F-B1AD456EA47E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C9AEB5-6C91-4B81-88F9-9E5B6EE5369E}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1340,7 +1362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0FE100-F3EB-445A-A31F-D6E5ECC5ABF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2B1786-7E80-43FA-9620-D8F810E020DE}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1571,17 +1593,17 @@
         <v>4</v>
       </c>
       <c r="C30" s="21">
-        <v>1175</v>
-      </c>
-      <c r="D30" s="8">
+        <v>1194</v>
+      </c>
+      <c r="D30" s="22">
         <f>B30*C30</f>
-        <v>4700</v>
-      </c>
-      <c r="E30" s="8">
+        <v>4776</v>
+      </c>
+      <c r="E30" s="22">
         <f>D30*12</f>
-        <v>56400</v>
-      </c>
-      <c r="F30" s="2" t="s">
+        <v>57312</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1593,17 +1615,17 @@
         <v>13</v>
       </c>
       <c r="C31" s="21">
-        <v>1678</v>
-      </c>
-      <c r="D31" s="8">
+        <v>1622</v>
+      </c>
+      <c r="D31" s="22">
         <f>B31*C31</f>
-        <v>21814</v>
-      </c>
-      <c r="E31" s="8">
+        <v>21086</v>
+      </c>
+      <c r="E31" s="22">
         <f>D31*12</f>
-        <v>261768</v>
-      </c>
-      <c r="F31" s="2" t="s">
+        <v>253032</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1615,17 +1637,17 @@
         <v>2</v>
       </c>
       <c r="C32" s="21">
-        <v>2266</v>
-      </c>
-      <c r="D32" s="8">
+        <v>2545</v>
+      </c>
+      <c r="D32" s="22">
         <f>B32*C32</f>
-        <v>4532</v>
-      </c>
-      <c r="E32" s="8">
+        <v>5090</v>
+      </c>
+      <c r="E32" s="22">
         <f>D32*12</f>
-        <v>54384</v>
-      </c>
-      <c r="F32" s="2" t="s">
+        <v>61080</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1637,39 +1659,39 @@
         <v>1</v>
       </c>
       <c r="C33" s="21">
-        <v>2266</v>
-      </c>
-      <c r="D33" s="8">
+        <v>2363</v>
+      </c>
+      <c r="D33" s="22">
         <f>B33*C33</f>
-        <v>2266</v>
-      </c>
-      <c r="E33" s="8">
+        <v>2363</v>
+      </c>
+      <c r="E33" s="22">
         <f>D33*12</f>
-        <v>27192</v>
-      </c>
-      <c r="F33" s="2" t="s">
+        <v>28356</v>
+      </c>
+      <c r="F33" s="23" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="25">
         <f>SUM(B30:B33)</f>
         <v>20</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="26">
         <f>IFERROR(D34/B34,"")</f>
-        <v>1665.6</v>
-      </c>
-      <c r="D34" s="24">
+        <v>1665.75</v>
+      </c>
+      <c r="D34" s="26">
         <f>SUM(D30:D33)</f>
-        <v>33312</v>
-      </c>
-      <c r="E34" s="24">
+        <v>33315</v>
+      </c>
+      <c r="E34" s="26">
         <f>SUM(E30:E33)</f>
-        <v>399744</v>
+        <v>399780</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1683,16 +1705,16 @@
       <c r="F36" s="14"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25" t="s">
+      <c r="A37" s="27"/>
+      <c r="B37" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25" t="s">
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1700,12 +1722,12 @@
       <c r="A38" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="8">
-        <v>399807.32177263958</v>
+      <c r="B38" s="22">
+        <v>399722</v>
       </c>
       <c r="C38" s="8">
         <f>E34</f>
-        <v>399744</v>
+        <v>399780</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>96</v>
@@ -1716,23 +1738,23 @@
         <v>97</v>
       </c>
       <c r="B39" s="8">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="C39" s="4">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="24" t="s">
         <v>98</v>
       </c>
       <c r="B40" s="8">
         <f>B38+B39</f>
-        <v>399807.32177263958</v>
+        <v>402722</v>
       </c>
       <c r="C40" s="8">
         <f>C38+C39</f>
-        <v>399744</v>
+        <v>402780</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1740,28 +1762,28 @@
         <v>99</v>
       </c>
       <c r="B41" s="8">
-        <f>-B38*0.03</f>
-        <v>-11994.219653179187</v>
+        <f>-B38*0.02</f>
+        <v>-7994.4400000000005</v>
       </c>
       <c r="C41" s="8">
         <f>-C38*Assumptions!$B$3</f>
-        <v>-11992.32</v>
+        <v>-11993.4</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="26">
         <f>B40+B41</f>
-        <v>387813.10211946041</v>
-      </c>
-      <c r="C42" s="24">
+        <v>394727.56</v>
+      </c>
+      <c r="C42" s="26">
         <f>C40+C41</f>
-        <v>387751.67999999999</v>
+        <v>390786.6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,22 +1797,22 @@
       <c r="F44" s="14"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="25" t="s">
+      <c r="D45" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F45" s="27" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1798,18 +1820,20 @@
       <c r="A46" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="8"/>
+      <c r="B46" s="22">
+        <v>48769</v>
+      </c>
       <c r="C46" s="8">
         <f>B22*Assumptions!$B$18</f>
         <v>49800</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="28">
         <f>C46</f>
         <v>49800</v>
       </c>
-      <c r="E46" s="8" t="str">
+      <c r="E46" s="8">
         <f t="shared" ref="E46:E54" si="0">IF(ISNUMBER(B46),D46-B46,"")</f>
-        <v/>
+        <v>1031</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>107</v>
@@ -1819,18 +1843,20 @@
       <c r="A47" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="8"/>
+      <c r="B47" s="22">
+        <v>29521</v>
+      </c>
       <c r="C47" s="8">
         <f>B7*Assumptions!$B$5+B8*Assumptions!$B$6</f>
         <v>18556</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="28">
         <f t="shared" ref="D47:D53" si="1">IF(ISNUMBER(B47),MAX(B47,C47),C47)</f>
-        <v>18556</v>
-      </c>
-      <c r="E47" s="8" t="str">
+        <v>29521</v>
+      </c>
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>109</v>
@@ -1840,18 +1866,20 @@
       <c r="A48" t="s">
         <v>110</v>
       </c>
-      <c r="B48" s="8"/>
+      <c r="B48" s="22">
+        <v>15989</v>
+      </c>
       <c r="C48" s="8">
         <f>C42*Assumptions!$B$4</f>
-        <v>19387.583999999999</v>
-      </c>
-      <c r="D48" s="26">
+        <v>19539.329999999998</v>
+      </c>
+      <c r="D48" s="28">
         <f t="shared" si="1"/>
-        <v>19387.583999999999</v>
-      </c>
-      <c r="E48" s="8" t="str">
+        <v>19539.329999999998</v>
+      </c>
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3550.3299999999981</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>111</v>
@@ -1861,18 +1889,20 @@
       <c r="A49" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="8"/>
+      <c r="B49" s="22">
+        <v>20000</v>
+      </c>
       <c r="C49" s="8">
         <f>B7*Assumptions!$B$7</f>
         <v>24000</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="28">
         <f t="shared" si="1"/>
         <v>24000</v>
       </c>
-      <c r="E49" s="8" t="str">
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>113</v>
@@ -1882,18 +1912,20 @@
       <c r="A50" t="s">
         <v>114</v>
       </c>
-      <c r="B50" s="8"/>
+      <c r="B50" s="22">
+        <v>32789</v>
+      </c>
       <c r="C50" s="8">
         <f>B7*Assumptions!$B$11</f>
         <v>32000</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="28">
         <f t="shared" si="1"/>
-        <v>32000</v>
-      </c>
-      <c r="E50" s="8" t="str">
+        <v>32789</v>
+      </c>
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>115</v>
@@ -1903,18 +1935,20 @@
       <c r="A51" t="s">
         <v>116</v>
       </c>
-      <c r="B51" s="8"/>
+      <c r="B51" s="22">
+        <v>6602</v>
+      </c>
       <c r="C51" s="8">
         <f>B7*Assumptions!$B$12</f>
         <v>8000</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="28">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1398</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>117</v>
@@ -1924,18 +1958,20 @@
       <c r="A52" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="8"/>
+      <c r="B52" s="22">
+        <v>20400</v>
+      </c>
       <c r="C52" s="8">
         <f>B7*Assumptions!$B$13</f>
         <v>5000</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="28">
         <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="E52" s="8" t="str">
+        <v>20400</v>
+      </c>
+      <c r="E52" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>119</v>
@@ -1945,12 +1981,12 @@
       <c r="A53" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="8"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="8">
         <f>B7*Assumptions!$B$14</f>
         <v>6000</v>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="28">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
@@ -1963,24 +1999,24 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="24">
-        <f>B42-B22*B25</f>
-        <v>167033.10211946041</v>
-      </c>
-      <c r="C54" s="24">
+      <c r="B54" s="26">
+        <f>SUM(B46:B53)</f>
+        <v>174070</v>
+      </c>
+      <c r="C54" s="26">
         <f>SUM(C46:C53)</f>
-        <v>162743.584</v>
-      </c>
-      <c r="D54" s="24">
+        <v>162895.33000000002</v>
+      </c>
+      <c r="D54" s="26">
         <f>SUM(D46:D53)</f>
-        <v>162743.584</v>
-      </c>
-      <c r="E54" s="24">
+        <v>190049.33000000002</v>
+      </c>
+      <c r="E54" s="26">
         <f t="shared" si="0"/>
-        <v>-4289.5181194604083</v>
+        <v>15979.330000000016</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>122</v>
@@ -1992,15 +2028,15 @@
       </c>
       <c r="B55" s="8">
         <f>IFERROR(B54/B7,"")</f>
-        <v>8351.6551059730209</v>
+        <v>8703.5</v>
       </c>
       <c r="C55" s="8">
         <f>IFERROR(C54/B7,"")</f>
-        <v>8137.1792000000005</v>
+        <v>8144.7665000000006</v>
       </c>
       <c r="D55" s="8">
         <f>IFERROR(D54/B7,"")</f>
-        <v>8137.1792000000005</v>
+        <v>9502.4665000000005</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2009,24 +2045,24 @@
       </c>
       <c r="B56" s="18">
         <f>IFERROR(B54/B42,"")</f>
-        <v>0.43070515463917514</v>
+        <v>0.44098770301217377</v>
       </c>
       <c r="C56" s="18">
         <f>IFERROR(C54/C42,"")</f>
-        <v>0.41971084174283912</v>
+        <v>0.41683959992486957</v>
       </c>
       <c r="D56" s="18">
         <f>IF(C38&gt;0,IFERROR(D54/C42,""),"")</f>
-        <v>0.41971084174283912</v>
+        <v>0.48632509405389035</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="B57" s="12" t="str">
+      <c r="B57" s="29" t="str">
         <f>IF(ISNUMBER(B54),IF(D54&gt;B54*(1+Assumptions!$B$24),"OM EXPENSES LIGHT","OM expenses reasonable"),"OM expenses not published")</f>
-        <v>OM expenses reasonable</v>
+        <v>OM EXPENSES LIGHT</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2040,77 +2076,80 @@
       <c r="F59" s="14"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="25"/>
-      <c r="B60" s="25" t="s">
+      <c r="A60" s="27"/>
+      <c r="B60" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C60" s="25" t="s">
+      <c r="C60" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25" t="s">
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="24">
+      <c r="B61" s="26">
         <f>B42-B54</f>
-        <v>220780</v>
-      </c>
-      <c r="C61" s="24">
+        <v>220657.56</v>
+      </c>
+      <c r="C61" s="26">
         <f>IF(C38&gt;0,C42-D54,"")</f>
-        <v>225008.09599999999</v>
+        <v>200737.26999999996</v>
+      </c>
+      <c r="F61" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="22" t="s">
-        <v>128</v>
+      <c r="A62" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="B62" s="18">
         <f>IFERROR(B61/B22,"")</f>
-        <v>5.3199999999999997E-2</v>
+        <v>5.3170496385542165E-2</v>
       </c>
       <c r="C62" s="18">
         <f>IF(C61="","",IFERROR(C61/B22,""))</f>
-        <v>5.4218818313253009E-2</v>
+        <v>4.8370426506024085E-2</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B63" s="19">
         <f>IFERROR(B22/B38,"")</f>
-        <v>10.380000000000003</v>
+        <v>10.38221563986971</v>
       </c>
       <c r="C63" s="19">
         <f>IF(C38&gt;0,IFERROR(B22/C38,""),"")</f>
-        <v>10.381644252321486</v>
+        <v>10.38070939016459</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B64" s="8">
         <f>IFERROR(B61/B7,"")</f>
-        <v>11039</v>
+        <v>11032.878000000001</v>
       </c>
       <c r="C64" s="8">
         <f>IF(C61="","",IFERROR(C61/B7,""))</f>
-        <v>11250.4048</v>
+        <v>10036.863499999998</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2120,7 +2159,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B67" s="8">
         <f>IFERROR(B22*Assumptions!$B$20,"")</f>
@@ -2129,43 +2168,43 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B68" s="8">
         <f>IF(C61="","",IFERROR(PV(Assumptions!$B$22/12,Assumptions!$B$23*12,-C61/Assumptions!$B$21/12),""))</f>
-        <v>2436271.0223045954</v>
+        <v>2173479.1000477313</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="22" t="s">
-        <v>135</v>
+      <c r="A69" s="24" t="s">
+        <v>136</v>
       </c>
       <c r="B69" s="8">
         <f>IFERROR(MIN(B67,B68),"")</f>
-        <v>2436271.0223045954</v>
+        <v>2173479.1000477313</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B70" s="8">
         <f>IFERROR(B22-B69,"")</f>
-        <v>1713728.9776954046</v>
+        <v>1976520.8999522687</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B71" s="8">
         <f>IFERROR(-PMT(Assumptions!$B$22/12,Assumptions!$B$23*12,B69)*12,"")</f>
-        <v>180006.47679999942</v>
+        <v>160589.81599999947</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B72" s="19">
         <f>IFERROR(C61/B71,"")</f>
@@ -2174,30 +2213,30 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B73" s="8">
         <f>IFERROR(C61-B71,"")</f>
-        <v>45001.619200000569</v>
+        <v>40147.454000000493</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B74" s="18">
         <f>IFERROR(B73/B70,"")</f>
-        <v>2.6259472638735459E-2</v>
+        <v>2.0312182887097231E-2</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{9C58F5A8-91A1-489A-A518-AA390FF3C31D}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{580E42C4-99C5-4FED-9547-D82BF8E3EBF9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>

--- a/files/17-900-n-orange-grove-ave.xlsx
+++ b/files/17-900-n-orange-grove-ave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iniculete\LAAA-Deploys\onmarket\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5F925DF-1DA0-47A1-B2B7-44444FE49FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1BA8BF9-8B45-4A8D-8EBB-C2FA5584B043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0FB7AB8E-E91A-4826-8E9C-AE1E3B28B9AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DFE67D4A-2381-4962-B145-734D0C401C16}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
     <t>Data pulled 9/17/2026 from LoopNet public listing + rent roll and expenses read from the listing broker's OM (Marcus &amp; Millichap, Aug 2026)</t>
   </si>
   <si>
-    <t>NOTE: First sale in 38 years | OM: Unit 21 (1 Bd / 1 Ba) is vacant; OM asking rent $2,300 used as its current rent, per OM convention (OM totals include it in scheduled rent).; Cross-check: sum of 20 unit rents = $33,311/mo ($399,732/yr) vs OM stated $33,310/mo and $399,722/yr GPR; difference is rounding, well within 1%.; Rent roll f | OM: Unit 21 (1 Bd / 1 Ba) is vacant; OM asking rent $2,300 used as its current rent, per OM convention (OM totals include it in scheduled rent).; Cross-check: sum of 20 unit rents = $33,311/mo ($399,732/yr) vs OM stated $33,310/mo and $399,722/yr GPR; difference is rounding, well within 1%.; Rent roll f</t>
+    <t>NOTE: First sale in 38 years | OM: Unit 21 (1 Bd / 1 Ba) is vacant; OM asking rent $2,300 used as its current rent, per OM convention (OM totals include it in scheduled rent).; Cross-check: sum of 20 unit rents = $33,311/mo ($399,732/yr) vs OM stated $33,310/mo and $399,722/yr GPR; difference is rounding, well within 1%.; Rent roll f</t>
   </si>
   <si>
     <t>PROPERTY</t>
@@ -682,7 +682,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69CC0E20-B427-41A2-9D1C-C18C64CC5E2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CB4B5B8-5DAD-4E06-BC36-E0223FD699E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -993,7 +993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C9AEB5-6C91-4B81-88F9-9E5B6EE5369E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBA0741-630B-477D-B6A2-6695C60A8B41}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1362,7 +1362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2B1786-7E80-43FA-9620-D8F810E020DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9796F748-4EF4-4187-A54B-8F051BF7912E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2236,7 +2236,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{580E42C4-99C5-4FED-9547-D82BF8E3EBF9}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{F5AA597E-328B-4CFA-8DD8-3724C58E4C48}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId2"/>
